--- a/matrix_file/fdk_matrix.xlsx
+++ b/matrix_file/fdk_matrix.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\dev\Carie Projects\FDK Triangle\fdk-triangulator\public\matrix_file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E08B5AEA-039D-4BAA-B9F4-107C3CA8BB40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE8EBB24-04AE-46D0-9D0C-C3051FD265A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-1140" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1366,10 +1366,6 @@
     <t>Navigation System: Very Feldenkraisian</t>
   </si>
   <si>
-    <t>The philosophy for our navigation system is resonant with the Feldenkrais method. It emphasizes exploration. Just as a Feldenkrais lesson Carie ostensibly teaches is actually your lesson, this 'Book of Feldenkrais' is your book. You get choose where you want to meander. In computer terms, this is a berry-picking approach—you create your own path on the hillside as you choose the next juicy idea that you are interested in exploring. For more on 'findability' see Ambient Findability (Morville) — https://www.alibris.com/Ambient-Findability-What-We-Find-Changes-Who-We-Become-Peter-Morville/book/40772935
-Our approach is certainly is non-linear!</t>
-  </si>
-  <si>
     <t>Navigation</t>
   </si>
   <si>
@@ -1594,6 +1590,10 @@
   </si>
   <si>
     <t>https://youtube.com/shorts/LjufMKwxB9A</t>
+  </si>
+  <si>
+    <t>The philosophy for our navigation system is resonant with the Feldenkrais method. It emphasizes exploration. Just as a Feldenkrais lesson Carie ostensibly teaches is actually your lesson, this 'Book of Feldenkrais' is your book. You get choose where you want to meander. In computer terms, this is a berry-picking approach—you create your own path on the hillside as you choose the next juicy idea that you are interested in exploring. For more on [findability](https://www.alibris.com/Ambient-Findability-What-We-Find-Changes-Who-We-Become-Peter-Morville/book/40772935), see Ambient Findability (Morville).
+Our approach is certainly is non-linear!</t>
   </si>
 </sst>
 </file>
@@ -54908,10 +54908,10 @@
         <v>15</v>
       </c>
       <c r="D118" s="8" t="s">
+        <v>515</v>
+      </c>
+      <c r="J118" s="7" t="s">
         <v>444</v>
-      </c>
-      <c r="J118" s="7" t="s">
-        <v>445</v>
       </c>
       <c r="N118" s="9" t="s">
         <v>387</v>
@@ -55325,7 +55325,7 @@
         <v>62</v>
       </c>
       <c r="EU118" s="6" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="EV118" s="6" t="s">
         <v>77</v>
@@ -55357,16 +55357,16 @@
         <v>117</v>
       </c>
       <c r="B119" s="7" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C119" s="7" t="s">
         <v>15</v>
       </c>
       <c r="D119" s="8" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="J119" s="7" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="N119" s="9" t="s">
         <v>387</v>
@@ -55806,16 +55806,16 @@
         <v>118</v>
       </c>
       <c r="B120" s="7" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C120" s="7" t="s">
         <v>15</v>
       </c>
       <c r="D120" s="8" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="J120" s="7" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="N120" s="9" t="s">
         <v>387</v>
@@ -56270,16 +56270,16 @@
         <v>119</v>
       </c>
       <c r="B121" s="7" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C121" s="7" t="s">
         <v>15</v>
       </c>
       <c r="D121" s="8" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="J121" s="7" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="N121" s="9" t="s">
         <v>387</v>
@@ -56719,16 +56719,16 @@
         <v>120</v>
       </c>
       <c r="B122" s="7" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C122" s="7" t="s">
         <v>15</v>
       </c>
       <c r="D122" s="8" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="J122" s="7" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="N122" s="9" t="s">
         <v>387</v>
@@ -57168,16 +57168,16 @@
         <v>121</v>
       </c>
       <c r="B123" s="7" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C123" s="7" t="s">
         <v>15</v>
       </c>
       <c r="D123" s="8" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="J123" s="7" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="N123" s="9" t="s">
         <v>387</v>
@@ -57617,16 +57617,16 @@
         <v>122</v>
       </c>
       <c r="B124" s="7" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C124" s="7" t="s">
         <v>15</v>
       </c>
       <c r="D124" s="8" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J124" s="7" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="N124" s="9" t="s">
         <v>387</v>
@@ -58066,16 +58066,16 @@
         <v>123</v>
       </c>
       <c r="B125" s="7" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C125" s="7" t="s">
         <v>15</v>
       </c>
       <c r="D125" s="8" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="J125" s="7" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="N125" s="9" t="s">
         <v>18</v>
@@ -58515,13 +58515,13 @@
         <v>124</v>
       </c>
       <c r="B126" s="7" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C126" s="7" t="s">
         <v>15</v>
       </c>
       <c r="D126" s="8" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="J126" s="7" t="s">
         <v>385</v>
@@ -58964,13 +58964,13 @@
         <v>125</v>
       </c>
       <c r="B127" s="7" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C127" s="7" t="s">
         <v>15</v>
       </c>
       <c r="D127" s="8" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="J127" s="7" t="s">
         <v>385</v>
@@ -59413,13 +59413,13 @@
         <v>126</v>
       </c>
       <c r="B128" s="7" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C128" s="7" t="s">
         <v>15</v>
       </c>
       <c r="D128" s="8" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="J128" s="7" t="s">
         <v>385</v>
@@ -59862,13 +59862,13 @@
         <v>127</v>
       </c>
       <c r="B129" s="7" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C129" s="7" t="s">
         <v>15</v>
       </c>
       <c r="D129" s="8" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="J129" s="7" t="s">
         <v>385</v>
@@ -60311,13 +60311,13 @@
         <v>128</v>
       </c>
       <c r="B130" s="7" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C130" s="7" t="s">
         <v>15</v>
       </c>
       <c r="D130" s="8" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="J130" s="7" t="s">
         <v>385</v>
@@ -60760,13 +60760,13 @@
         <v>129</v>
       </c>
       <c r="B131" s="7" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C131" s="7" t="s">
         <v>15</v>
       </c>
       <c r="D131" s="8" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="J131" s="7" t="s">
         <v>385</v>
@@ -61209,13 +61209,13 @@
         <v>130</v>
       </c>
       <c r="B132" s="7" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C132" s="7" t="s">
         <v>15</v>
       </c>
       <c r="D132" s="8" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="J132" s="7" t="s">
         <v>385</v>
@@ -61658,13 +61658,13 @@
         <v>131</v>
       </c>
       <c r="B133" s="7" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C133" s="7" t="s">
         <v>15</v>
       </c>
       <c r="D133" s="8" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="J133" s="7" t="s">
         <v>385</v>
@@ -62107,13 +62107,13 @@
         <v>132</v>
       </c>
       <c r="B134" s="7" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C134" s="7" t="s">
         <v>15</v>
       </c>
       <c r="D134" s="8" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="J134" s="7" t="s">
         <v>385</v>
@@ -62556,13 +62556,13 @@
         <v>133</v>
       </c>
       <c r="B135" s="7" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C135" s="7" t="s">
         <v>15</v>
       </c>
       <c r="D135" s="8" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="J135" s="7" t="s">
         <v>385</v>
@@ -63011,13 +63011,13 @@
         <v>134</v>
       </c>
       <c r="B136" s="7" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C136" s="7" t="s">
         <v>15</v>
       </c>
       <c r="D136" s="8" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="J136" s="7" t="s">
         <v>385</v>
@@ -63466,16 +63466,16 @@
         <v>135</v>
       </c>
       <c r="B137" s="6" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C137" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D137" s="6" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="J137" s="6" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="N137" s="6" t="s">
         <v>387</v>
@@ -63901,7 +63901,7 @@
         <v>0</v>
       </c>
       <c r="EY137" s="6" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="EZ137" s="6">
         <v>0</v>
@@ -63921,16 +63921,16 @@
         <v>136</v>
       </c>
       <c r="B138" s="6" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C138" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D138" s="6" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="J138" s="6" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="N138" s="6" t="s">
         <v>387</v>
@@ -64284,7 +64284,7 @@
         <v>0</v>
       </c>
       <c r="EA138" s="6" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="EB138" s="6" t="s">
         <v>277</v>
@@ -64370,16 +64370,16 @@
         <v>137</v>
       </c>
       <c r="B139" s="6" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C139" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D139" s="6" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="J139" s="6" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="N139" s="6" t="s">
         <v>387</v>
@@ -64819,16 +64819,16 @@
         <v>138</v>
       </c>
       <c r="B140" s="6" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C140" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D140" s="6" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="J140" s="6" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="N140" s="6" t="s">
         <v>387</v>
@@ -65268,16 +65268,16 @@
         <v>139</v>
       </c>
       <c r="B141" s="6" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C141" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D141" s="6" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="J141" s="6" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="N141" s="6" t="s">
         <v>387</v>
@@ -65717,16 +65717,16 @@
         <v>140</v>
       </c>
       <c r="B142" s="6" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C142" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D142" s="6" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="J142" s="6" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="N142" s="6" t="s">
         <v>387</v>
@@ -66137,7 +66137,7 @@
         <v>0</v>
       </c>
       <c r="ET142" s="6" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="EU142" s="6" t="s">
         <v>71</v>
@@ -66166,16 +66166,16 @@
         <v>141</v>
       </c>
       <c r="B143" s="6" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C143" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D143" s="6" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="J143" s="6" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="N143" s="6" t="s">
         <v>387</v>
@@ -66615,16 +66615,16 @@
         <v>142</v>
       </c>
       <c r="B144" s="6" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C144" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D144" s="6" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="J144" s="6" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="N144" s="6" t="s">
         <v>387</v>
@@ -67064,19 +67064,19 @@
         <v>147</v>
       </c>
       <c r="B145" s="6" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C145" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D145" s="6" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="J145" s="6" t="s">
         <v>220</v>
       </c>
       <c r="K145" s="6" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="N145" s="6" t="s">
         <v>387</v>
@@ -67525,19 +67525,19 @@
         <v>148</v>
       </c>
       <c r="B146" s="6" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C146" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D146" s="6" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="J146" s="6" t="s">
         <v>220</v>
       </c>
       <c r="K146" s="6" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="N146" s="6" t="s">
         <v>387</v>
@@ -67998,19 +67998,19 @@
         <v>149</v>
       </c>
       <c r="B147" s="6" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C147" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D147" s="6" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="J147" s="6" t="s">
         <v>220</v>
       </c>
       <c r="K147" s="6" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="N147" s="6" t="s">
         <v>387</v>
@@ -68465,19 +68465,19 @@
         <v>150</v>
       </c>
       <c r="B148" s="6" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C148" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D148" s="6" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="J148" s="6" t="s">
         <v>220</v>
       </c>
       <c r="K148" s="6" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="N148" s="6" t="s">
         <v>387</v>
@@ -68932,19 +68932,19 @@
         <v>151</v>
       </c>
       <c r="B149" s="6" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C149" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D149" s="6" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="J149" s="6" t="s">
         <v>220</v>
       </c>
       <c r="K149" s="6" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="N149" s="6" t="s">
         <v>387</v>
@@ -69408,13 +69408,13 @@
         <v>152</v>
       </c>
       <c r="B150" s="6" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="C150" s="6" t="s">
         <v>400</v>
       </c>
       <c r="F150" s="6" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="J150" s="6" t="s">
         <v>403</v>
@@ -69881,13 +69881,13 @@
         <v>153</v>
       </c>
       <c r="B151" s="6" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C151" s="6" t="s">
         <v>400</v>
       </c>
       <c r="F151" s="6" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="J151" s="6" t="s">
         <v>403</v>
@@ -70354,13 +70354,13 @@
         <v>154</v>
       </c>
       <c r="B152" s="6" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C152" s="6" t="s">
         <v>400</v>
       </c>
       <c r="F152" s="6" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="J152" s="6" t="s">
         <v>403</v>

--- a/matrix_file/fdk_matrix.xlsx
+++ b/matrix_file/fdk_matrix.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\dev\Carie Projects\FDK Triangle\fdk-triangulator\public\matrix_file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE8EBB24-04AE-46D0-9D0C-C3051FD265A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{908B7313-FDAB-4A29-A9EC-E7C850C5D83C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-1140" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1592,7 +1592,7 @@
     <t>https://youtube.com/shorts/LjufMKwxB9A</t>
   </si>
   <si>
-    <t>The philosophy for our navigation system is resonant with the Feldenkrais method. It emphasizes exploration. Just as a Feldenkrais lesson Carie ostensibly teaches is actually your lesson, this 'Book of Feldenkrais' is your book. You get choose where you want to meander. In computer terms, this is a berry-picking approach—you create your own path on the hillside as you choose the next juicy idea that you are interested in exploring. For more on [findability](https://www.alibris.com/Ambient-Findability-What-We-Find-Changes-Who-We-Become-Peter-Morville/book/40772935), see Ambient Findability (Morville).
+    <t>The philosophy for our navigation system is resonant with the Feldenkrais method. It emphasizes exploration. Just as a Feldenkrais lesson Carie ostensibly teaches is actually your lesson, this 'Book of Feldenkrais' is your book. You get choose where you want to meander. In computer terms, this is a berry-picking approach—you create your own path on the hillside as you choose the next juicy idea that you are interested in exploring. For more on findability, see [Ambient Findability(Morville)](https://www.alibris.com/Ambient-Findability-What-We-Find-Changes-Who-We-Become-Peter-Morville/book/40772935).
 Our approach is certainly is non-linear!</t>
   </si>
 </sst>
